--- a/tests/TestTrack/Testes.xlsx
+++ b/tests/TestTrack/Testes.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\My Drive\UNI\2025\2025-2Sem\LDS - Lab Dev Soft\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\My Drive\UNI\2025\2025-2Sem\LDS - Lab Dev Soft\Dev\main\stock-manager\tests\TestTrack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CA190F-94CB-43CA-A68A-AF85339892C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BB800B-7E77-4A97-86AF-BB563B2791E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{255F9818-EC5A-46FF-9D2F-15463B870A74}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="689" firstSheet="4" activeTab="6" xr2:uid="{255F9818-EC5A-46FF-9D2F-15463B870A74}"/>
   </bookViews>
   <sheets>
-    <sheet name="Check_T1T2" sheetId="1" r:id="rId1"/>
-    <sheet name="CheckT3_20260419" sheetId="2" r:id="rId2"/>
-    <sheet name="CheckT3_20260426" sheetId="4" r:id="rId3"/>
-    <sheet name="TestsT4" sheetId="3" r:id="rId4"/>
+    <sheet name="Resumo" sheetId="5" r:id="rId1"/>
+    <sheet name="Check_T1T2" sheetId="1" r:id="rId2"/>
+    <sheet name="CheckT3_20260419" sheetId="2" r:id="rId3"/>
+    <sheet name="CheckT3_20260426" sheetId="4" r:id="rId4"/>
+    <sheet name="CheckT4_20260428" sheetId="8" r:id="rId5"/>
+    <sheet name="Tests T4" sheetId="3" r:id="rId6"/>
+    <sheet name="Plano de Testes (Minuta)" sheetId="6" r:id="rId7"/>
+    <sheet name="Plano de Testes (Controlo)" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CheckT3_20260419!$A$1:$K$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CheckT3_20260426!$B$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CheckT3_20260419!$A$1:$K$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">CheckT3_20260426!$B$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">CheckT4_20260428!$B$1:$K$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="456">
   <si>
     <t>Foi possível verificar bem a versão final, mas não reconstruir todo o percurso intermédio entre versões com detalhe total.</t>
   </si>
@@ -676,13 +681,748 @@
   </si>
   <si>
     <t>A View está focada em leitura de input, apresentação de output e emissão de eventos; não contém lógica de negócio</t>
+  </si>
+  <si>
+    <t>Plano de testes</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Descrição</t>
+  </si>
+  <si>
+    <t>Dados de Input</t>
+  </si>
+  <si>
+    <t>Resultado esperado</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Introduzido por</t>
+  </si>
+  <si>
+    <t>Introduzido em:</t>
+  </si>
+  <si>
+    <t>Corrido em:</t>
+  </si>
+  <si>
+    <t>Resultado Obtido</t>
+  </si>
+  <si>
+    <t>Aspectos gerais</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Instancia view e model</t>
+  </si>
+  <si>
+    <t>MostrarMenu</t>
+  </si>
+  <si>
+    <t>MostrarStock</t>
+  </si>
+  <si>
+    <t>Faz encaminhamento</t>
+  </si>
+  <si>
+    <t>view.OpcaoSelecionada += ProcessarOpcao;</t>
+  </si>
+  <si>
+    <t>model.OperacaoConcluida += view.MostrarConfirmacao;</t>
+  </si>
+  <si>
+    <t>Em consulta e reposição</t>
+  </si>
+  <si>
+    <t>No diagrama</t>
+  </si>
+  <si>
+    <t>O Controller deve estar funcional ao nível do arranque</t>
+  </si>
+  <si>
+    <t>Em caso de erro de validação</t>
+  </si>
+  <si>
+    <t>A View deve suportar menu</t>
+  </si>
+  <si>
+    <t>Classe com Nome</t>
+  </si>
+  <si>
+    <t>Implementar lógica de actualização</t>
+  </si>
+  <si>
+    <t>O projecto deve declarar a dependência necessária para Json.NET</t>
+  </si>
+  <si>
+    <t>Existe a pasta tests e um README a dizer que ali ficarão testes</t>
+  </si>
+  <si>
+    <t>A View está bem separada do domínio</t>
+  </si>
+  <si>
+    <t>Definir cenários de consulta</t>
+  </si>
+  <si>
+    <t>A integração estrutural existe</t>
+  </si>
+  <si>
+    <t>Mapear os testes: plano de testes preenchido com base na minuta (Moodle)</t>
+  </si>
+  <si>
+    <t>Registo do Verificador / minuta Moodle</t>
+  </si>
+  <si>
+    <t>O plano de testes deve estar preenchido por tipo de teste</t>
+  </si>
+  <si>
+    <t>Plano de testes unitários - View</t>
+  </si>
+  <si>
+    <t>View.cs / plano de testes</t>
+  </si>
+  <si>
+    <t>Devem estar definidos casos de teste unitário da View orientados a input/output</t>
+  </si>
+  <si>
+    <t>Plano de testes unitários - Controller</t>
+  </si>
+  <si>
+    <t>Controller.cs / plano de testes</t>
+  </si>
+  <si>
+    <t>Devem estar definidos casos de teste unitário do Controller para encaminhamento</t>
+  </si>
+  <si>
+    <t>Plano de testes unitários - Model</t>
+  </si>
+  <si>
+    <t>Model.cs / plano de testes</t>
+  </si>
+  <si>
+    <t>Devem estar definidos casos de teste unitário do Model para consulta</t>
+  </si>
+  <si>
+    <t>Plano de testes de integração MVC</t>
+  </si>
+  <si>
+    <t>Controller.cs / View.cs / Model.cs / plano de testes</t>
+  </si>
+  <si>
+    <t>Devem estar definidos cenários integrados View -&gt; Controller -&gt; Model -&gt; View</t>
+  </si>
+  <si>
+    <t>Há cenários principais identificados</t>
+  </si>
+  <si>
+    <t>Excepções</t>
+  </si>
+  <si>
+    <t>Plano de testes de excepções / robustez MVC</t>
+  </si>
+  <si>
+    <t>Devem estar definidos cenários de erro coerentes com MVC e distribuídos pelos componentes</t>
+  </si>
+  <si>
+    <t>Há cenários de erro já conhecidos (opção inválida</t>
+  </si>
+  <si>
+    <t>Testes unitários da View executados</t>
+  </si>
+  <si>
+    <t>Próprio projecto / View.cs</t>
+  </si>
+  <si>
+    <t>Devem existir evidências de execução dos testes unitários da View</t>
+  </si>
+  <si>
+    <t>Não existem ainda registos formais de execução isolada da View</t>
+  </si>
+  <si>
+    <t>O trabalho formal de testes unitários da View ainda não arrancou</t>
+  </si>
+  <si>
+    <t>Executar após fecho da matriz de testes e registar resultados no plano</t>
+  </si>
+  <si>
+    <t>Próprio projecto / Controller.cs</t>
+  </si>
+  <si>
+    <t>Devem existir evidências de execução dos testes unitários do Controller</t>
+  </si>
+  <si>
+    <t>Não existem ainda registos formais de execução isolada do Controller</t>
+  </si>
+  <si>
+    <t>O trabalho formal de testes unitários do Controller ainda não arrancou</t>
+  </si>
+  <si>
+    <t>Executar e registar cenários de encaminhamento</t>
+  </si>
+  <si>
+    <t>Próprio projecto / Model.cs</t>
+  </si>
+  <si>
+    <t>Devem existir evidências de execução dos testes unitários do Model</t>
+  </si>
+  <si>
+    <t>Não existem ainda registos formais de execução isolada do Model</t>
+  </si>
+  <si>
+    <t>O trabalho formal de testes unitários do Model ainda não arrancou</t>
+  </si>
+  <si>
+    <t>Executar e registar cenários de consulta</t>
+  </si>
+  <si>
+    <t>Testes de integração MVC executados</t>
+  </si>
+  <si>
+    <t>Devem existir evidências de execução dos fluxos principais ponta-a-ponta</t>
+  </si>
+  <si>
+    <t>Existe validação manual preliminar registada pela equipa: opção inválida (7 e abc)</t>
+  </si>
+  <si>
+    <t>Testes de excepções / robustez executados</t>
+  </si>
+  <si>
+    <t>Devem existir evidências de execução de cenários de erro coerentes com MVC</t>
+  </si>
+  <si>
+    <t>Existe validação manual preliminar de opção inválida</t>
+  </si>
+  <si>
+    <t>Excepções implementadas respeitam o estilo MVC em todos os componentes</t>
+  </si>
+  <si>
+    <t>Controller.cs / Model.cs / View.cs</t>
+  </si>
+  <si>
+    <t>O tratamento de erros não deve ficar concentrado só num componente e deve respeitar as responsabilidades MVC</t>
+  </si>
+  <si>
+    <t>Opção inválida e dados inválidos são tratados no Controller; stock insuficiente é tratado no Model e apresentado pela View</t>
+  </si>
+  <si>
+    <t>Falta confirmação formal do tratamento coerente de erros técnicos de persistência e da sua apresentação ao utilizador</t>
+  </si>
+  <si>
+    <t>Definir e registar política mínima para erros técnicos e confirmar a sua distribuição pelos componentes</t>
+  </si>
+  <si>
+    <t>Verificação final: coerência entre diagramas</t>
+  </si>
+  <si>
+    <t>Verificação de conformidade MVC + apoio à validação e testes de integração entre componentes</t>
+  </si>
+  <si>
+    <t>Código + fluxos MVC + registo do Verificador</t>
+  </si>
+  <si>
+    <t>O fluxo deve manter-se coerente com MVC durante a validação integrada entre componentes</t>
+  </si>
+  <si>
+    <t>A base MVC está estável</t>
+  </si>
+  <si>
+    <t>MVCArranque da aplicaçãoProgram.csProgram apenas arranca o Controller</t>
+  </si>
+  <si>
+    <t>MVCArranque no ControllerController.csO ciclo da aplicação deve iniciar no Controller e passar para a View</t>
+  </si>
+  <si>
+    <t>MVCController como ponto central de ligaçãoController.csO Controller deve instanciar e ligar View e Model</t>
+  </si>
+  <si>
+    <t>MVCInput entra na ViewView.csA variante Curry &amp; Grace exige input na View</t>
+  </si>
+  <si>
+    <t>MVCView não conhece directamente o ModelView.csA View não deve instanciar nem referenciar directamente o Model</t>
+  </si>
+  <si>
+    <t>MVCModel não conhece View nem ControllerModel.csO Model não deve depender de View nem Controller</t>
+  </si>
+  <si>
+    <t>MVCSaída apresentada pela ViewView.csOs resultados devem ser apresentados na View</t>
+  </si>
+  <si>
+    <t>MVCPapel do Controller limitado à coordenaçãoController.csO Controller não deve conter lógica de negócio do domínio</t>
+  </si>
+  <si>
+    <t>Eventos/DelegadosInput da View chega ao Controller por eventosController.csOs inputs do utilizador devem ser recebidos pelo Controller via eventos</t>
+  </si>
+  <si>
+    <t>Eventos/DelegadosPedidos de consulta e reposição estão ligados por delegadosController.cs / View.csOs pedidos de leitura devem estar formalmente ligados no arranque</t>
+  </si>
+  <si>
+    <t>Eventos/DelegadosNotificações do Model chegam à View por eventosController.csAs respostas do Model devem chegar à View por eventos</t>
+  </si>
+  <si>
+    <t>Eventos/DelegadosInvocação segura de eventos na ViewView.csA View deve invocar eventos com verificação nula</t>
+  </si>
+  <si>
+    <t>AcoplamentoAusência de acoplamento estrutural View -&gt; ModelView.csA View não deve criar nem conhecer o Model</t>
+  </si>
+  <si>
+    <t>AcoplamentoAusência de acoplamento estrutural Model -&gt; View/ControllerModel.csO Model deve estar isolado dos outros componentes</t>
+  </si>
+  <si>
+    <t>AcoplamentoMediação explícita do Controller nos fluxos de leituraController.cs / arquitecturaOs fluxos principais devem passar explicitamente pelo Controller</t>
+  </si>
+  <si>
+    <t>DocumentaçãoCoerência com a variante Curry &amp; Grace adoptadaCódigo + decisão da equipaO código deve manter input na View e coordenação geral no Controller</t>
+  </si>
+  <si>
+    <t>DocumentaçãoCoerência entre código e diagrama de sequência V5Controller.cs / View.cs / diagrama V5O fluxo implementado deve coincidir com o fluxo documentado</t>
+  </si>
+  <si>
+    <t>ImplementaçãoEstrutura base do Controller implementadaController.csO Controller deve estar funcional ao nível do arranque, coordenação e encerramento</t>
+  </si>
+  <si>
+    <t>ImplementaçãoCiclo do menu sem recursão acumuladaController.cs / View.csO fluxo principal não deve acumular chamadas recursivas ao menu</t>
+  </si>
+  <si>
+    <t>ImplementaçãoMenu não duplicado em casos de erro de validaçãoController.csEm caso de erro de validação, o menu não deve ser reapresentado duas vezes</t>
+  </si>
+  <si>
+    <t>ImplementaçãoEstrutura base da View implementadaView.csA View deve suportar menu, recolha de input e apresentação de output</t>
+  </si>
+  <si>
+    <t>ImplementaçãoLeitura válida de inteiros na ViewView.csA View deve validar input numérico básico</t>
+  </si>
+  <si>
+    <t>ImplementaçãoClasse de dados Produto definidaProduto.csDeve existir uma estrutura de dados para o domínio</t>
+  </si>
+  <si>
+    <t>ImplementaçãoMétodos de consulta do Model implementadosModel.csSolicitarListaProdutos e SolicitarListaReposicao devem estar funcionais</t>
+  </si>
+  <si>
+    <t>ImplementaçãoMétodos de lógica de negócio do Model implementadosModel.csRegistarOuAtualizarProduto e RemoverQuantidade devem estar funcionais</t>
+  </si>
+  <si>
+    <t>ImplementaçãoPersistência JSON implementadaModel.csCarregarDados e GuardarDados devem estar funcionais</t>
+  </si>
+  <si>
+    <t>ImplementaçãoDependência da API JSON declarada no projectoGestorStockDomestico.csprojO projecto deve declarar a dependência necessária para Json.NET, se a persistência a usar for mesmo essa</t>
+  </si>
+  <si>
+    <t>ImplementaçãoPasta de testes preparadatests/README.mdA área de testes deve ter pelo menos estrutura mínima identificada</t>
+  </si>
+  <si>
+    <t>TestesPlano de testes unitáriosRegisto do VerificadorDevem estar definidos casos de teste para Controller e Model</t>
+  </si>
+  <si>
+    <t>TestesTestes unitários do Controller executadosPróprio projectoDeve existir validação do encaminhamento e subscrição dos fluxos</t>
+  </si>
+  <si>
+    <t>TestesTestes unitários do Model executadosPróprio projectoDeve existir validação da lógica de negócio e persistência</t>
+  </si>
+  <si>
+    <t>TestesTestabilidade da ViewView.csA View deve manter-se focada em input/output para não dificultar validação posterior</t>
+  </si>
+  <si>
+    <t>TestesPlano de testes de integraçãoRegisto do VerificadorDevem estar definidos cenários View -&gt; Controller -&gt; Model -&gt; View</t>
+  </si>
+  <si>
+    <t>TestesTestes de integração executadosPróprio projectoOs fluxos principais devem ser validados ponta-a-ponta</t>
+  </si>
+  <si>
+    <t>Equipa: 11- Codezilla</t>
+  </si>
+  <si>
+    <t>UM1</t>
+  </si>
+  <si>
+    <t>Registar novo produto</t>
+  </si>
+  <si>
+    <t>UM2</t>
+  </si>
+  <si>
+    <t>Actualizar produto existente</t>
+  </si>
+  <si>
+    <t>UM3</t>
+  </si>
+  <si>
+    <t>Remover quantidade com stock suficiente</t>
+  </si>
+  <si>
+    <t>UM4</t>
+  </si>
+  <si>
+    <t>Remover quantidade com stock insuficiente</t>
+  </si>
+  <si>
+    <t>UM5</t>
+  </si>
+  <si>
+    <t>Gerar lista de reposição</t>
+  </si>
+  <si>
+    <t>UM6</t>
+  </si>
+  <si>
+    <t>Testes unitários - Model</t>
+  </si>
+  <si>
+    <t>UC1</t>
+  </si>
+  <si>
+    <t>Opção inválida no menu</t>
+  </si>
+  <si>
+    <t>UC2</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>UC3</t>
+  </si>
+  <si>
+    <t>Registo com dados inválidos</t>
+  </si>
+  <si>
+    <t>Nome vazio ou quantidade &lt;= 0</t>
+  </si>
+  <si>
+    <t>UC4</t>
+  </si>
+  <si>
+    <t>Remoção com dados inválidos</t>
+  </si>
+  <si>
+    <t>UC5</t>
+  </si>
+  <si>
+    <t>Encerramento controlado</t>
+  </si>
+  <si>
+    <t>Testes unitários - Controller</t>
+  </si>
+  <si>
+    <t>Testes de integração - fluxos principais MVC</t>
+  </si>
+  <si>
+    <t>IM1</t>
+  </si>
+  <si>
+    <t>Fluxo completo de registo e consulta</t>
+  </si>
+  <si>
+    <t>O produto aparece correctamente no stock</t>
+  </si>
+  <si>
+    <t>IM2</t>
+  </si>
+  <si>
+    <t>Fluxo completo de remoção válida</t>
+  </si>
+  <si>
+    <t>IM3</t>
+  </si>
+  <si>
+    <t>Fluxo completo de remoção com erro</t>
+  </si>
+  <si>
+    <t>Produto com stock insuficiente</t>
+  </si>
+  <si>
+    <t>IM4</t>
+  </si>
+  <si>
+    <t>Produtos abaixo do mínimo</t>
+  </si>
+  <si>
+    <t>IM5</t>
+  </si>
+  <si>
+    <t>Saída controlada</t>
+  </si>
+  <si>
+    <t>ER1</t>
+  </si>
+  <si>
+    <t>ER2</t>
+  </si>
+  <si>
+    <t>Texto inválido no menu</t>
+  </si>
+  <si>
+    <t>ER3</t>
+  </si>
+  <si>
+    <t>Quantidade negativa ou zero</t>
+  </si>
+  <si>
+    <t>ER4</t>
+  </si>
+  <si>
+    <t>ER5</t>
+  </si>
+  <si>
+    <t>Repetição da lista de reposição</t>
+  </si>
+  <si>
+    <t>Escolher várias vezes a opção 4</t>
+  </si>
+  <si>
+    <t>Testes de validação / excepções / robustez</t>
+  </si>
+  <si>
+    <t>LR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criado/Testado por: </t>
+  </si>
+  <si>
+    <t>PN</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>UV1</t>
+  </si>
+  <si>
+    <t>Menu aceita opção válida de consulta</t>
+  </si>
+  <si>
+    <t>É emitido o evento OpcaoSelecionada com o valor "1"</t>
+  </si>
+  <si>
+    <t>UV2</t>
+  </si>
+  <si>
+    <t>Menu aceita opção válida de saída</t>
+  </si>
+  <si>
+    <t>É emitido o evento OpcaoSelecionada com o valor "9"</t>
+  </si>
+  <si>
+    <t>UV3</t>
+  </si>
+  <si>
+    <t>Leitura de inteiro rejeita texto inválido</t>
+  </si>
+  <si>
+    <t>abc, depois 5</t>
+  </si>
+  <si>
+    <t>A View mostra mensagem de erro e só aceita o valor inteiro válido</t>
+  </si>
+  <si>
+    <t>UV4</t>
+  </si>
+  <si>
+    <t>Leitura de inteiro rejeita vazio</t>
+  </si>
+  <si>
+    <t>"", depois 2</t>
+  </si>
+  <si>
+    <t>A View insiste até receber inteiro válido</t>
+  </si>
+  <si>
+    <t>UV5</t>
+  </si>
+  <si>
+    <t>Pedido de dados de produto emite evento correcto</t>
+  </si>
+  <si>
+    <t>Nome=Arroz, Quantidade=10, Mínimo=3, Unidade=kg</t>
+  </si>
+  <si>
+    <t>É emitido DadosProdutoIntroduzidos com os valores recolhidos</t>
+  </si>
+  <si>
+    <t>UV6</t>
+  </si>
+  <si>
+    <t>Pedido de remoção emite evento correcto</t>
+  </si>
+  <si>
+    <t>Nome=Arroz, Quantidade=4</t>
+  </si>
+  <si>
+    <t>É emitido RemocaoSolicitada com os valores recolhidos</t>
+  </si>
+  <si>
+    <t>UV7</t>
+  </si>
+  <si>
+    <t>Mostrar stock apresenta lista sem alterar dados</t>
+  </si>
+  <si>
+    <t>Lista com produtos válidos</t>
+  </si>
+  <si>
+    <t>A View apresenta os produtos e não altera o estado recebido</t>
+  </si>
+  <si>
+    <t>UV8</t>
+  </si>
+  <si>
+    <t>Mostrar lista de reposição apresenta apenas os dados recebidos</t>
+  </si>
+  <si>
+    <t>Lista de reposição recebida do Model</t>
+  </si>
+  <si>
+    <t>A View limita-se a apresentar os dados</t>
+  </si>
+  <si>
+    <t>UV9</t>
+  </si>
+  <si>
+    <t>Mostrar erro apresenta mensagem sem lógica adicional</t>
+  </si>
+  <si>
+    <t>"Stock insuficiente"</t>
+  </si>
+  <si>
+    <t>A View apresenta a mensagem e não assume lógica do Model</t>
+  </si>
+  <si>
+    <t>UV10</t>
+  </si>
+  <si>
+    <t>Mostrar confirmação apresenta mensagem final da operação</t>
+  </si>
+  <si>
+    <t>"Produto registado com sucesso"</t>
+  </si>
+  <si>
+    <t>A View apresenta a confirmação e termina o fluxo visual correctamente</t>
+  </si>
+  <si>
+    <t>Testes unitários - View</t>
+  </si>
+  <si>
+    <t>Mensagem de erro e continuidade normal do menu</t>
+  </si>
+  <si>
+    <t>Erro apresentado sem duplicação do menu</t>
+  </si>
+  <si>
+    <t>Erro apresentado sem crash</t>
+  </si>
+  <si>
+    <t>Comportamento estável, sem duplicação anómala</t>
+  </si>
+  <si>
+    <t>Registar Arroz, 10, 3, kg; depois consultar</t>
+  </si>
+  <si>
+    <t>Produto com stock suficiente</t>
+  </si>
+  <si>
+    <t>Stock actualizado e confirmação apresentada</t>
+  </si>
+  <si>
+    <t>Fluxo de lista de reposição</t>
+  </si>
+  <si>
+    <t>Lista apresentada correctamente</t>
+  </si>
+  <si>
+    <t>Aplicação encerra de forma controlada</t>
+  </si>
+  <si>
+    <t>Arroz, 10, 3, kg</t>
+  </si>
+  <si>
+    <t>Produto adicionado, persistência actualizada, confirmação emitida</t>
+  </si>
+  <si>
+    <t>Arroz, 15, 4, kg</t>
+  </si>
+  <si>
+    <t>Produto actualizado sem duplicação</t>
+  </si>
+  <si>
+    <t>Produto com 10, remover 4</t>
+  </si>
+  <si>
+    <t>Quantidade final 6, confirmação emitida</t>
+  </si>
+  <si>
+    <t>Produto com 2, remover 5</t>
+  </si>
+  <si>
+    <t>Não altera stock, erro emitido</t>
+  </si>
+  <si>
+    <t>Produtos acima e abaixo do mínimo</t>
+  </si>
+  <si>
+    <t>Só devolve os produtos abaixo do mínimo</t>
+  </si>
+  <si>
+    <t>Carregar dados JSON</t>
+  </si>
+  <si>
+    <t>Ficheiro válido</t>
+  </si>
+  <si>
+    <t>Lista interna carregada correctamente</t>
+  </si>
+  <si>
+    <t>UM7</t>
+  </si>
+  <si>
+    <t>Guardar dados JSON</t>
+  </si>
+  <si>
+    <t>Lista com produtos</t>
+  </si>
+  <si>
+    <t>Ficheiro actualizado correctamente</t>
+  </si>
+  <si>
+    <t>Opção inválida numérica</t>
+  </si>
+  <si>
+    <t>O Controller manda a View apresentar erro</t>
+  </si>
+  <si>
+    <t>O Controller rejeita e manda a View apresentar erro</t>
+  </si>
+  <si>
+    <t>O Controller acciona o fecho controlado</t>
+  </si>
+  <si>
+    <t>Encaminhamento de registo válido</t>
+  </si>
+  <si>
+    <t>Dados válidos de produto</t>
+  </si>
+  <si>
+    <t>O Controller encaminha correctamente para o Model</t>
+  </si>
+  <si>
+    <t>UC6</t>
+  </si>
+  <si>
+    <t>Encaminhamento de remoção válida</t>
+  </si>
+  <si>
+    <t>Nome e quantidade válidos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -706,6 +1446,83 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -724,10 +1541,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -751,11 +1569,96 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{612E69E9-5A3E-4472-B949-4157E02DDDF1}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -766,6 +1669,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{394F472F-BA34-40BA-97D2-4060CCFDF27D}" name="Table1" displayName="Table1" ref="A1:I22" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowCellStyle="Normal 2">
+  <autoFilter ref="A1:I22" xr:uid="{394F472F-BA34-40BA-97D2-4060CCFDF27D}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{2C7870E8-9AB5-4232-9401-1075123CB322}" name="ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{CF1921F0-48CF-441B-8A43-300957470D29}" name="Descrição" dataDxfId="7">
+      <calculatedColumnFormula>_xlfn.XLOOKUP($A2,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{BBE88039-91AE-455F-A7C3-2CF2B687531F}" name="Dados de Input" dataDxfId="6">
+      <calculatedColumnFormula>_xlfn.XLOOKUP($A2,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{9B59D6E7-0ABF-4F2D-BA49-4C61FCAED498}" name="Resultado esperado" dataDxfId="5">
+      <calculatedColumnFormula>_xlfn.XLOOKUP($A2,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{037692BF-C725-4887-A765-D5BB269778FF}" name="Introduzido por" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{66FA6F5A-B3E2-41AC-A487-CFF5BDBAA2A2}" name="Introduzido em:" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{C862B575-65F4-4D24-B965-8CA7E55DDC39}" name="Criado/Testado por: " dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{631FD125-E751-4C1E-95D3-00B2F088621D}" name="Corrido em:" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{0557674D-B274-4146-B316-4E2C1E27A82E}" name="Resultado Obtido" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1084,6 +2011,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57E4E80-F95D-4D64-8887-B16866BD77DB}">
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="9">
+        <v>46131</v>
+      </c>
+      <c r="E2" s="9">
+        <v>46138</v>
+      </c>
+      <c r="F2" s="9">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5ED22D-2303-481F-BAFB-5A97F828FD35}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1192,7 +2180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F526CA-B3E2-43A2-AB52-FE2D25F4D0A2}">
   <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="28" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1240,7 +2228,7 @@
       </c>
       <c r="L1" s="3"/>
     </row>
-    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1270,8 +2258,12 @@
       <c r="K2" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="L2" s="6" t="str">
+        <f>B2&amp;C2&amp;D2&amp;E2</f>
+        <v>MVCArranque da aplicaçãoProgram.csProgram apenas arranca o Controller</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -1299,8 +2291,12 @@
       <c r="K3" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="L3" s="6" t="str">
+        <f t="shared" ref="L3:L36" si="0">B3&amp;C3&amp;D3&amp;E3</f>
+        <v>MVCArranque no ControllerController.csO ciclo da aplicação deve iniciar no Controller e passar para a View</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1328,8 +2324,12 @@
       <c r="K4" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="L4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>MVCController como ponto central de ligaçãoController.csO Controller deve instanciar e ligar View e Model</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1357,8 +2357,12 @@
       <c r="K5" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="L5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>MVCInput entra na ViewView.csA variante Curry &amp; Grace exige input na View</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1386,8 +2390,12 @@
       <c r="K6" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="L6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>MVCView não conhece directamente o ModelView.csA View não deve instanciar nem referenciar directamente o Model</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -1415,8 +2423,12 @@
       <c r="K7" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="L7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>MVCModel não conhece View nem ControllerModel.csO Model não deve depender de View nem Controller</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -1444,8 +2456,12 @@
       <c r="K8" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="L8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>MVCSaída apresentada pela ViewView.csOs resultados devem ser apresentados na View</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -1472,6 +2488,10 @@
       </c>
       <c r="K9" s="7">
         <v>46131</v>
+      </c>
+      <c r="L9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>MVCPapel do Controller limitado à coordenaçãoController.csO Controller não deve conter lógica de negócio do domínio</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="90" x14ac:dyDescent="0.25">
@@ -1502,8 +2522,12 @@
       <c r="K10" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="L10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Eventos/DelegadosInput da View chega ao Controller por eventosController.csOs inputs do utilizador devem ser recebidos pelo Controller via eventos</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -1537,8 +2561,12 @@
       <c r="K11" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="L11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Eventos/DelegadosPedidos de consulta e reposição estão ligados por delegadosController.cs / View.csOs pedidos de leitura devem estar formalmente ligados no arranque</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -1566,8 +2594,12 @@
       <c r="K12" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="L12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Eventos/DelegadosNotificações do Model chegam à View por eventosController.csAs respostas do Model devem chegar à View por eventos</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -1595,8 +2627,12 @@
       <c r="K13" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="L13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Eventos/DelegadosInvocação segura de eventos na ViewView.csA View deve invocar eventos com verificação nula</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -1624,8 +2660,12 @@
       <c r="K14" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="L14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>AcoplamentoAusência de acoplamento estrutural View -&gt; ModelView.csA View não deve criar nem conhecer o Model</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -1653,8 +2693,12 @@
       <c r="K15" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="L15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>AcoplamentoAusência de acoplamento estrutural Model -&gt; View/ControllerModel.csO Model deve estar isolado dos outros componentes</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -1688,8 +2732,12 @@
       <c r="K16" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>AcoplamentoMediação explícita do Controller nos fluxos de leituraController.cs / arquitecturaOs fluxos principais devem passar explicitamente pelo Controller</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -1717,8 +2765,12 @@
       <c r="K17" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="L17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>DocumentaçãoCoerência com a variante Curry &amp; Grace adoptadaCódigo + decisão da equipaO código deve manter input na View e coordenação geral no Controller</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -1752,8 +2804,12 @@
       <c r="K18" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="L18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>DocumentaçãoCoerência entre código e diagrama de sequência V5Controller.cs / View.cs / diagrama V5O fluxo implementado deve coincidir com o fluxo documentado</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -1787,8 +2843,12 @@
       <c r="K19" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="L19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoEstrutura base do Controller implementadaController.csO Controller deve estar funcional ao nível do arranque, coordenação e encerramento</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -1822,8 +2882,12 @@
       <c r="K20" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="L20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoCiclo do menu sem recursão acumuladaController.cs / View.csO fluxo principal não deve acumular chamadas recursivas ao menu</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -1857,8 +2921,12 @@
       <c r="K21" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoMenu não duplicado em casos de erro de validaçãoController.csEm caso de erro de validação, o menu não deve ser reapresentado duas vezes</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>21</v>
       </c>
@@ -1886,8 +2954,12 @@
       <c r="K22" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoEstrutura base da View implementadaView.csA View deve suportar menu, recolha de input e apresentação de output</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -1915,8 +2987,12 @@
       <c r="K23" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoLeitura válida de inteiros na ViewView.csA View deve validar input numérico básico</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -1944,8 +3020,12 @@
       <c r="K24" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="L24" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoClasse de dados Produto definidaProduto.csDeve existir uma estrutura de dados para o domínio</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -1979,8 +3059,12 @@
       <c r="K25" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="L25" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoMétodos de consulta do Model implementadosModel.csSolicitarListaProdutos e SolicitarListaReposicao devem estar funcionais</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -2014,8 +3098,12 @@
       <c r="K26" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoMétodos de lógica de negócio do Model implementadosModel.csRegistarOuAtualizarProduto e RemoverQuantidade devem estar funcionais</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -2049,8 +3137,12 @@
       <c r="K27" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="L27" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoPersistência JSON implementadaModel.csCarregarDados e GuardarDados devem estar funcionais</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="120" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>27</v>
       </c>
@@ -2084,8 +3176,12 @@
       <c r="K28" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="L28" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoDependência da API JSON declarada no projectoGestorStockDomestico.csprojO projecto deve declarar a dependência necessária para Json.NET, se a persistência a usar for mesmo essa</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -2119,8 +3215,12 @@
       <c r="K29" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="L29" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoPasta de testes preparadatests/README.mdA área de testes deve ter pelo menos estrutura mínima identificada</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>29</v>
       </c>
@@ -2154,8 +3254,12 @@
       <c r="K30" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="L30" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>TestesPlano de testes unitáriosRegisto do VerificadorDevem estar definidos casos de teste para Controller e Model</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -2189,8 +3293,12 @@
       <c r="K31" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="L31" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>TestesTestes unitários do Controller executadosPróprio projectoDeve existir validação do encaminhamento e subscrição dos fluxos</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>31</v>
       </c>
@@ -2224,8 +3332,12 @@
       <c r="K32" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="L32" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>TestesTestes unitários do Model executadosPróprio projectoDeve existir validação da lógica de negócio e persistência</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -2259,8 +3371,12 @@
       <c r="K33" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="L33" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>TestesTestabilidade da ViewView.csA View deve manter-se focada em input/output para não dificultar validação posterior</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>33</v>
       </c>
@@ -2294,8 +3410,12 @@
       <c r="K34" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="L34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>TestesPlano de testes de integraçãoRegisto do VerificadorDevem estar definidos cenários View -&gt; Controller -&gt; Model -&gt; View</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -2329,9 +3449,17 @@
       <c r="K35" s="7">
         <v>46131</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L35" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>TestesTestes de integração executadosPróprio projectoOs fluxos principais devem ser validados ponta-a-ponta</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K36" s="7"/>
+      <c r="L36" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K36" xr:uid="{28F526CA-B3E2-43A2-AB52-FE2D25F4D0A2}"/>
@@ -2339,7 +3467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7F2CFB3-FD0D-43E4-9DF9-DBEFDAAF4C7B}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="28" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2388,9 +3516,9 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="6">
         <f>_xlfn.XLOOKUP(L2,CheckT3_20260419!L:L,CheckT3_20260419!A:A)</f>
-        <v>ID#</v>
+        <v>15</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>46</v>
@@ -2420,13 +3548,17 @@
         <v>49</v>
       </c>
       <c r="K2" s="7">
-        <v>46132</v>
+        <v>46138</v>
+      </c>
+      <c r="L2" s="6" t="str">
+        <f>B2&amp;C2&amp;D2&amp;E2</f>
+        <v>AcoplamentoMediação explícita do Controller nos fluxos de leituraController.cs / arquitecturaOs fluxos principais devem passar explicitamente pelo Controller</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="str">
+      <c r="A3" s="6">
         <f>_xlfn.XLOOKUP(L3,CheckT3_20260419!L:L,CheckT3_20260419!A:A)</f>
-        <v>ID#</v>
+        <v>17</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>50</v>
@@ -2456,13 +3588,17 @@
         <v>49</v>
       </c>
       <c r="K3" s="7">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="str">
+        <v>46138</v>
+      </c>
+      <c r="L3" s="6" t="str">
+        <f t="shared" ref="L3:L11" si="0">B3&amp;C3&amp;D3&amp;E3</f>
+        <v>DocumentaçãoCoerência entre código e diagrama de sequência V5Controller.cs / View.cs / diagrama V5O fluxo implementado deve coincidir com o fluxo documentado</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
         <f>_xlfn.XLOOKUP(L4,CheckT3_20260419!L:L,CheckT3_20260419!A:A)</f>
-        <v>ID#</v>
+        <v>19</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>52</v>
@@ -2486,13 +3622,17 @@
         <v>34</v>
       </c>
       <c r="K4" s="7">
-        <v>46136</v>
+        <v>46138</v>
+      </c>
+      <c r="L4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoCiclo do menu sem recursão acumuladaController.cs / View.csO fluxo principal não deve acumular chamadas recursivas ao menu</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="str">
+      <c r="A5" s="6">
         <f>_xlfn.XLOOKUP(L5,CheckT3_20260419!L:L,CheckT3_20260419!A:A)</f>
-        <v>ID#</v>
+        <v>20</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>52</v>
@@ -2516,13 +3656,17 @@
         <v>34</v>
       </c>
       <c r="K5" s="7">
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="str">
+        <v>46138</v>
+      </c>
+      <c r="L5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoMenu não duplicado em casos de erro de validaçãoController.csEm caso de erro de validação, o menu não deve ser reapresentado duas vezes</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <f>_xlfn.XLOOKUP(L6,CheckT3_20260419!L:L,CheckT3_20260419!A:A)</f>
-        <v>ID#</v>
+        <v>24</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>52</v>
@@ -2552,13 +3696,17 @@
         <v>34</v>
       </c>
       <c r="K6" s="7">
-        <v>46141</v>
+        <v>46138</v>
+      </c>
+      <c r="L6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoMétodos de consulta do Model implementadosModel.csSolicitarListaProdutos e SolicitarListaReposicao devem estar funcionais</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="str">
+      <c r="A7" s="6">
         <f>_xlfn.XLOOKUP(L7,CheckT3_20260419!L:L,CheckT3_20260419!A:A)</f>
-        <v>ID#</v>
+        <v>25</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>52</v>
@@ -2588,13 +3736,17 @@
         <v>34</v>
       </c>
       <c r="K7" s="7">
-        <v>46142</v>
+        <v>46138</v>
+      </c>
+      <c r="L7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoMétodos de lógica de negócio do Model implementadosModel.csRegistarOuAtualizarProduto e RemoverQuantidade devem estar funcionais</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="str">
+      <c r="A8" s="6">
         <f>_xlfn.XLOOKUP(L8,CheckT3_20260419!L:L,CheckT3_20260419!A:A)</f>
-        <v>ID#</v>
+        <v>26</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>52</v>
@@ -2624,13 +3776,17 @@
         <v>34</v>
       </c>
       <c r="K8" s="7">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="str">
+        <v>46138</v>
+      </c>
+      <c r="L8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoPersistência JSON implementadaModel.csCarregarDados e GuardarDados devem estar funcionais</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <f>_xlfn.XLOOKUP(L9,CheckT3_20260419!L:L,CheckT3_20260419!A:A)</f>
-        <v>ID#</v>
+        <v>27</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>52</v>
@@ -2654,13 +3810,17 @@
         <v>34</v>
       </c>
       <c r="K9" s="7">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="str">
+        <v>46138</v>
+      </c>
+      <c r="L9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoDependência da API JSON declarada no projectoGestorStockDomestico.csprojO projecto deve declarar a dependência necessária para Json.NET, se a persistência a usar for mesmo essa</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <f>_xlfn.XLOOKUP(L10,CheckT3_20260419!L:L,CheckT3_20260419!A:A)</f>
-        <v>ID#</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>52</v>
@@ -2690,10 +3850,14 @@
         <v>39</v>
       </c>
       <c r="K10" s="7">
-        <v>46145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>46138</v>
+      </c>
+      <c r="L10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>ImplementaçãoPasta de testes preparadatests/README.mdA área de testes deve ter pelo menos estrutura mínima identificada</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>32</v>
       </c>
@@ -2719,7 +3883,11 @@
         <v>34</v>
       </c>
       <c r="K11" s="7">
-        <v>46149</v>
+        <v>46138</v>
+      </c>
+      <c r="L11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>TestesTestabilidade da ViewView.csA View deve manter-se focada em input/output para não dificultar validação posterior.</v>
       </c>
     </row>
   </sheetData>
@@ -2728,11 +3896,4994 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28F1FE1-C94C-4884-A511-2881E79A94A6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B95FE683-E02E-4C54-A0AA-A6923C10F92D}">
+  <dimension ref="A1:L49"/>
+  <sheetFormatPr defaultColWidth="28" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="28" style="6"/>
+    <col min="5" max="5" width="34.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="28" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="7">
+        <v>46138</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="7">
+        <v>46138</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="7">
+        <v>46138</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="7">
+        <v>46138</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="7">
+        <v>46138</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="7">
+        <v>46138</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="7">
+        <v>46138</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="7">
+        <v>46138</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" s="7">
+        <v>46138</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="7">
+        <v>46138</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K34" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K35" s="7">
+        <v>46131</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="K37" s="7"/>
+    </row>
+    <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K42" s="6">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K47" s="6">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B1:K11" xr:uid="{E7F2CFB3-FD0D-43E4-9DF9-DBEFDAAF4C7B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28F1FE1-C94C-4884-A511-2881E79A94A6}">
+  <dimension ref="A1:K49"/>
+  <sheetFormatPr defaultColWidth="24.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="24.42578125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="K8" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="K9" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="K10" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32" s="7">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K42" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K47" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19965C5A-3877-4FE7-B091-2377A88C9E91}">
+  <dimension ref="A1:Z1020"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" style="17" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="70" style="17" customWidth="1"/>
+    <col min="5" max="26" width="8.7109375" style="17" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+    </row>
+    <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+    </row>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" s="17">
+        <v>1</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7" s="17">
+        <v>9</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+    </row>
+    <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+    </row>
+    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="C29" s="17">
+        <v>7</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="C32" s="17">
+        <v>9</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>454</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+    </row>
+    <row r="37" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="C42" s="17">
+        <v>9</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+    </row>
+    <row r="45" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="C46" s="17">
+        <v>7</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1006" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1007" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1008" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1009" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1011" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1012" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1013" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1014" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1015" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1016" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1017" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1018" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1019" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1020" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFF4CFEB-3CE3-4EEB-8004-53C1C29A12B7}">
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultRowHeight="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" style="6" customWidth="1"/>
+    <col min="2" max="3" width="33.5703125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="41.140625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="20" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B2" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A2,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Registar novo produto</v>
+      </c>
+      <c r="C2" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A2,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Arroz, 10, 3, kg</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A2,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Produto adicionado, persistência actualizada, confirmação emitida</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46140</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="H2" s="7">
+        <v>46138</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A3,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Actualizar produto existente</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A3,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Arroz, 15, 4, kg</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A3,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Produto actualizado sem duplicação</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A4,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Remover quantidade com stock suficiente</v>
+      </c>
+      <c r="C4" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A4,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Produto com 10, remover 4</v>
+      </c>
+      <c r="D4" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A4,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Quantidade final 6, confirmação emitida</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A5,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Remover quantidade com stock insuficiente</v>
+      </c>
+      <c r="C5" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A5,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Produto com 2, remover 5</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A5,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Não altera stock, erro emitido</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B6" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A6,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Gerar lista de reposição</v>
+      </c>
+      <c r="C6" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A6,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Produtos acima e abaixo do mínimo</v>
+      </c>
+      <c r="D6" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A6,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Só devolve os produtos abaixo do mínimo</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B7" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A7,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Carregar dados JSON</v>
+      </c>
+      <c r="C7" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A7,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Ficheiro válido</v>
+      </c>
+      <c r="D7" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A7,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Lista interna carregada correctamente</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A8,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Opção inválida numérica</v>
+      </c>
+      <c r="C8" s="6">
+        <f>_xlfn.XLOOKUP($A8,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>7</v>
+      </c>
+      <c r="D8" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A8,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>O Controller manda a View apresentar erro</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B9" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A9,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Registo com dados inválidos</v>
+      </c>
+      <c r="C9" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A9,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Nome vazio ou quantidade &lt;= 0</v>
+      </c>
+      <c r="D9" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A9,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>O Controller rejeita e manda a View apresentar erro</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="B10" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A10,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Remoção com dados inválidos</v>
+      </c>
+      <c r="C10" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A10,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Nome vazio ou quantidade &lt;= 0</v>
+      </c>
+      <c r="D10" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A10,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>O Controller rejeita e manda a View apresentar erro</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B11" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A11,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Encerramento controlado</v>
+      </c>
+      <c r="C11" s="6">
+        <f>_xlfn.XLOOKUP($A11,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>9</v>
+      </c>
+      <c r="D11" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A11,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>O Controller acciona o fecho controlado</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F11" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B12" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A12,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Encaminhamento de registo válido</v>
+      </c>
+      <c r="C12" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A12,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Dados válidos de produto</v>
+      </c>
+      <c r="D12" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A12,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>O Controller encaminha correctamente para o Model</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B13" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A13,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Fluxo completo de registo e consulta</v>
+      </c>
+      <c r="C13" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A13,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Registar Arroz, 10, 3, kg; depois consultar</v>
+      </c>
+      <c r="D13" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A13,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>O produto aparece correctamente no stock</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B14" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A14,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Fluxo completo de remoção válida</v>
+      </c>
+      <c r="C14" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A14,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Produto com stock suficiente</v>
+      </c>
+      <c r="D14" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A14,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Stock actualizado e confirmação apresentada</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F14" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="B15" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A15,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Fluxo completo de remoção com erro</v>
+      </c>
+      <c r="C15" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A15,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Produto com stock insuficiente</v>
+      </c>
+      <c r="D15" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A15,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Erro apresentado sem crash</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F15" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B16" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A16,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Fluxo de lista de reposição</v>
+      </c>
+      <c r="C16" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A16,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Produtos abaixo do mínimo</v>
+      </c>
+      <c r="D16" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A16,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Lista apresentada correctamente</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F16" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B17" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A17,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Saída controlada</v>
+      </c>
+      <c r="C17" s="6">
+        <f>_xlfn.XLOOKUP($A17,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>9</v>
+      </c>
+      <c r="D17" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A17,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Aplicação encerra de forma controlada</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F17" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B18" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A18,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Opção inválida no menu</v>
+      </c>
+      <c r="C18" s="6">
+        <f>_xlfn.XLOOKUP($A18,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>7</v>
+      </c>
+      <c r="D18" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A18,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Mensagem de erro e continuidade normal do menu</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F18" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B19" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A19,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Texto inválido no menu</v>
+      </c>
+      <c r="C19" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A19,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>abc</v>
+      </c>
+      <c r="D19" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A19,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Mensagem de erro e continuidade normal do menu</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F19" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B20" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A20,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Registo com dados inválidos</v>
+      </c>
+      <c r="C20" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A20,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Quantidade negativa ou zero</v>
+      </c>
+      <c r="D20" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A20,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Erro apresentado sem duplicação do menu</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F20" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B21" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A21,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Remoção com dados inválidos</v>
+      </c>
+      <c r="C21" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A21,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Quantidade negativa ou zero</v>
+      </c>
+      <c r="D21" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A21,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Erro apresentado sem crash</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F21" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B22" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A22,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!B:B)</f>
+        <v>Repetição da lista de reposição</v>
+      </c>
+      <c r="C22" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A22,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!C:C)</f>
+        <v>Escolher várias vezes a opção 4</v>
+      </c>
+      <c r="D22" s="6" t="str">
+        <f>_xlfn.XLOOKUP($A22,'Plano de Testes (Minuta)'!$A:$A,'Plano de Testes (Minuta)'!D:D)</f>
+        <v>Comportamento estável, sem duplicação anómala</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F22" s="7">
+        <v>46140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>